--- a/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T12:24:35+00:00</t>
+    <t>2026-06-10T14:04:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T14:04:02+00:00</t>
+    <t>2026-06-11T07:11:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T07:11:16+00:00</t>
+    <t>2026-06-11T07:24:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T07:24:18+00:00</t>
+    <t>2026-06-11T08:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T08:11:11+00:00</t>
+    <t>2026-06-11T08:38:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T08:38:12+00:00</t>
+    <t>2026-06-11T08:46:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T08:46:08+00:00</t>
+    <t>2026-06-11T09:21:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T09:21:46+00:00</t>
+    <t>2026-06-11T09:55:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
+++ b/Mechanisms-mapping-version-2/ig/CdaBLToBooleanConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T09:55:14+00:00</t>
+    <t>2026-06-11T09:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
